--- a/Result/profitability/2009.xlsx
+++ b/Result/profitability/2009.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.125</v>
+        <v>0.08375</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74125</v>
+        <v>2.87125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1</v>
+        <v>0.135</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2425</v>
+        <v>3.8675</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1225</v>
+        <v>0.15875</v>
       </c>
       <c r="N4" t="n">
-        <v>2.395</v>
+        <v>3.8425</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.15125</v>
+        <v>-0.09375</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.443750000000001</v>
+        <v>-6.097500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.18625</v>
+        <v>-0.22</v>
       </c>
       <c r="N6" t="n">
-        <v>-11.325</v>
+        <v>-9.658750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.165</v>
+        <v>-0.13125</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.643750000000001</v>
+        <v>-7.358750000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.84</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05999999999999998</v>
+        <v>-0.0525</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.295000000000002</v>
+        <v>-6.038750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.7</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001250000000000001</v>
+        <v>0.001249999999999987</v>
       </c>
       <c r="N9" t="n">
         <v>-5.596250000000001</v>
@@ -1648,7 +1648,7 @@
         <v>0.05624999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.333750000000002</v>
+        <v>-4.333750000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>0.23</v>
       </c>
       <c r="M11" t="n">
-        <v>0.035</v>
+        <v>0.03499999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.376250000000002</v>
+        <v>-4.376250000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.42</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06624999999999999</v>
+        <v>0.06624999999999998</v>
       </c>
       <c r="N12" t="n">
         <v>-3.602500000000001</v>
@@ -9836,6 +9836,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>892</v>
+      </c>
+      <c r="D75" t="n">
+        <v>773</v>
+      </c>
+      <c r="E75" t="n">
+        <v>118</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>102</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>98</v>
+      </c>
+      <c r="K75" t="n">
+        <v>98</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.52375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06000000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.049999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1825467497773818</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.421052631578947</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-3.418943533697632</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
